--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_SHEEP_ROCKY_MOUNTAIN_EWE.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_SHEEP_ROCKY_MOUNTAIN_EWE.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,19 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F1B0F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +109,23 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -135,11 +161,25 @@
         <color rgb="00B8895F"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,6 +213,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,163 +629,163 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>2026 SHEEP ROCKY MOUNTAIN EWE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1"/>
+    <row r="2" ht="40" customHeight="1"/>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Hunt Name</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Hunt Code</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Hunt Type</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>Res</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Non-Res</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Box Elder, Newfoundland Mtn</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>RE1000</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Ewe</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Rocky Mountain Bighorn Sheep</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>General Season</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Sep 08 2025 - Sep 16 2025</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="18" t="n">
         <v>2025</v>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr"/>
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -732,9 +796,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Georgia,Bold"&amp;12 2026 SHEEP ROCKY MOUNTAIN EWE</oddHeader>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
